--- a/src/main/java/com/mycompany/ocxrst/BASES/DIAS.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/DIAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{271E7EBD-9A19-4EBF-A372-1864FB71C02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD85F87-EF10-439A-BDBA-D65A1D7567B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C551862E-9A6C-4B04-BC49-104ED5471277}"/>
+    <workbookView xWindow="3120" yWindow="1200" windowWidth="14400" windowHeight="8170" xr2:uid="{C551862E-9A6C-4B04-BC49-104ED5471277}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,9 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>DIAS</t>
+  </si>
+  <si>
+    <t>--</t>
   </si>
 </sst>
 </file>
@@ -74,8 +77,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -410,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE990263-B3DA-4A70-B5B3-2CBE0CDC94F4}">
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.6328125" bestFit="1" customWidth="1"/>
@@ -422,157 +426,162 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33">
         <v>31</v>
       </c>
     </row>
